--- a/Actividades/INFORME DE ACTIVIDADES - copia.xlsx
+++ b/Actividades/INFORME DE ACTIVIDADES - copia.xlsx
@@ -12,23 +12,51 @@
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
-    <sheet name="Informe Febrero 26" sheetId="23" r:id="rId1"/>
+    <sheet name="Informe Febrero 26" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
+    <t>INFORME DE TAREAS POR CADA UNA DE LA ACTIVIDADES DEL CONTRATO DE PRESTACIÓN DE SERVICIOS</t>
+  </si>
+  <si>
+    <t>No. CONVENIO O CONTRATO:</t>
+  </si>
+  <si>
+    <t>{{NRO_CONTRATO}}</t>
+  </si>
+  <si>
+    <t>OBJETO DEL CONTRATO:</t>
+  </si>
+  <si>
+    <t>{{OBJETO}}</t>
+  </si>
+  <si>
+    <t>NOMBRE DEL CONTRATISTA:</t>
+  </si>
+  <si>
+    <t>{{NOMBRE_CONTRATISTA}}</t>
+  </si>
+  <si>
+    <t>No DE IDENTIFICACIÓN:</t>
+  </si>
+  <si>
+    <t>{{CEDULA}}</t>
+  </si>
+  <si>
+    <t>FECHA DE ACTIVIDADES:</t>
+  </si>
+  <si>
+    <t>{{RANGO_FECHAS}}</t>
+  </si>
+  <si>
+    <t>TIPO DE ACTIVIDAD</t>
+  </si>
+  <si>
     <t>FECHA</t>
   </si>
   <si>
@@ -44,9 +72,6 @@
     <t>MEDIO DE SOLICITUD</t>
   </si>
   <si>
-    <t>TIPO DE ACTIVIDAD</t>
-  </si>
-  <si>
     <t>CUMPLIDO</t>
   </si>
   <si>
@@ -54,46 +79,13 @@
   </si>
   <si>
     <t>OBSERVACIONES</t>
-  </si>
-  <si>
-    <t>INFORME DE TAREAS POR CADA UNA DE LA ACTIVIDADES DEL CONTRATO DE PRESTACIÓN DE SERVICIOS</t>
-  </si>
-  <si>
-    <t>No. CONVENIO O CONTRATO:</t>
-  </si>
-  <si>
-    <t>OBJETO DEL CONTRATO:</t>
-  </si>
-  <si>
-    <t>NOMBRE DEL CONTRATISTA:</t>
-  </si>
-  <si>
-    <t>No DE IDENTIFICACIÓN:</t>
-  </si>
-  <si>
-    <t>FECHA DE ACTIVIDADES:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha de informe:  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elaborado por:     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                                    Contratista</t>
-  </si>
-  <si>
-    <t>Vo Bo:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                                   Supervisor contrato</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,6 +120,22 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -143,7 +151,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -190,80 +198,95 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -271,22 +294,20 @@
   </cellStyles>
   <dxfs count="22">
     <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <name val="Arial"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -300,22 +321,20 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center"/>
     </dxf>
     <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <name val="Arial"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="164" formatCode="dd\-mmm\-yy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -331,21 +350,19 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center"/>
     </dxf>
     <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <name val="Arial"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -361,22 +378,20 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <name val="Arial"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -392,21 +407,19 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <name val="Arial"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -422,21 +435,19 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <name val="Arial"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -452,21 +463,19 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <name val="Arial"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -482,22 +491,20 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <name val="Arial"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="164" formatCode="dd\-mmm\-yy"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -513,22 +520,19 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <name val="Arial"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <border outline="0">
         <left/>
         <right style="thin">
           <color indexed="64"/>
@@ -553,14 +557,12 @@
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <name val="Arial"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -572,18 +574,15 @@
     <dxf>
       <font>
         <b/>
-        <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color theme="1"/>
         <name val="Arial"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <fill>
@@ -592,8 +591,8 @@
           <bgColor theme="0" tint="-0.249977111117893"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -904,568 +903,569 @@
   <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="43.28515625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" style="16" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" style="4" customWidth="1"/>
-    <col min="8" max="8" width="19.28515625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="39.85546875" style="4" customWidth="1"/>
-    <col min="10" max="10" width="0.140625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="26.42578125" style="4" customWidth="1"/>
-    <col min="12" max="16384" width="11.42578125" style="4"/>
+    <col min="1" max="1" width="43.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="19.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="39.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="0.140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="26.42578125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-    </row>
-    <row r="3" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="22"/>
+    <row r="1" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="20"/>
+    </row>
+    <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="20"/>
+    </row>
+    <row r="3" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="20"/>
+      <c r="C3" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="20"/>
+    </row>
+    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="20"/>
+    </row>
+    <row r="5" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="20"/>
+      <c r="C5" s="27" t="s">
+        <v>8</v>
+      </c>
       <c r="D5" s="22"/>
       <c r="E5" s="22"/>
       <c r="F5" s="22"/>
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
       <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="17" t="s">
+      <c r="J5" s="20"/>
+    </row>
+    <row r="6" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="20"/>
+    </row>
+    <row r="7" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-    </row>
-    <row r="7" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+      <c r="E7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
+      <c r="F7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="13"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="26"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
+      <c r="A10" s="16"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
     </row>
     <row r="13" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="15"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="11"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="11"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="8"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="11"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="8"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="11"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="8"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="11"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="8"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="11"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="8"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="11"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="8"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="11"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="8"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="11"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="8"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="11"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="8"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="11"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="8"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="11"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="8"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="11"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="8"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="11"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="8"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="11"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="8"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="11"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="8"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="11"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="8"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="11"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="8"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="11"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="8"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="11"/>
+      <c r="A33" s="9"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="8"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="11"/>
+      <c r="A34" s="9"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="8"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="11"/>
+      <c r="A35" s="9"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="8"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="11"/>
+      <c r="A36" s="9"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="8"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="11"/>
+      <c r="A37" s="9"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="8"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="11"/>
+      <c r="A38" s="9"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="8"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="11"/>
+      <c r="A39" s="9"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="8"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="11"/>
+      <c r="A40" s="9"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="8"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="13"/>
-      <c r="J41" s="11"/>
+      <c r="A41" s="9"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C3:J3"/>
     <mergeCell ref="B10:J10"/>
-    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="C6:J6"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C2:J2"/>
+    <mergeCell ref="B9:J9"/>
+    <mergeCell ref="C5:J5"/>
     <mergeCell ref="B12:J12"/>
     <mergeCell ref="B13:J13"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:J5"/>
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:J6"/>
-    <mergeCell ref="B9:J9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:J4"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:J2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:J3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="73" fitToHeight="0" orientation="landscape" r:id="rId1"/>
